--- a/DataTables/Datas/battle.hero.xlsx
+++ b/DataTables/Datas/battle.hero.xlsx
@@ -439,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -457,8 +457,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name_i18n_key</t>
+        </is>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -468,6 +470,11 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>view_prefab_address</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -489,6 +496,11 @@
       <c r="F2" t="s">
         <v>7</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -502,8 +514,10 @@
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Name i18n key</t>
+        </is>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -513,14 +527,21 @@
       </c>
       <c r="F4" t="s">
         <v>15</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>View Prefab Address</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>battle.hero.test_warrior.name</t>
+        </is>
       </c>
       <c r="D5">
         <v>30</v>
@@ -530,6 +551,11 @@
       </c>
       <c r="F5">
         <v>1001</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Runtime/Character/Prefabs/pfb_char_player.prefab</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/battle.hero.xlsx
+++ b/DataTables/Datas/battle.hero.xlsx
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,13 +98,123 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -121,8 +231,41 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -451,108 +594,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="1">
         <v>1</v>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="1">
         <is>
           <t>name_i18n_key</t>
         </is>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="1">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t>view_prefab_address</t>
         </is>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr" s="2">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="4">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="4">
         <v>11</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr" s="4">
         <is>
           <t>Name i18n key</t>
         </is>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr" s="4">
         <is>
           <t>View Prefab Address</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="6">
         <v>1001</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr" s="7">
         <is>
           <t>battle.hero.test_warrior.name</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>30</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="10">
         <v>1001</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr" s="11">
         <is>
           <t>Assets/Arts/Runtime/Character/Prefabs/pfb_char_player.prefab</t>
         </is>

--- a/DataTables/Datas/battle.hero.xlsx
+++ b/DataTables/Datas/battle.hero.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2963770b4e2416a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae947acf4b104459"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56,7 +56,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -72,8 +72,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="等线"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="28">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -163,6 +169,51 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F1F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF365F91"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F8FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF365F91"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E6E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F9F4"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -174,7 +225,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -210,6 +261,54 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -419,6 +518,13 @@
     <x:col min="4" max="4" width="10.875" customWidth="1"/>
     <x:col min="5" max="5" width="13.125" customWidth="1"/>
     <x:col min="6" max="6" width="12.75" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -445,6 +551,27 @@
       <x:c r="G1" s="1" t="str">
         <x:v>view_prefab_key</x:v>
       </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>initial_energy</x:v>
+      </x:c>
+      <x:c r="I1" s="13" t="str">
+        <x:v>max_energy</x:v>
+      </x:c>
+      <x:c r="J1" s="13" t="str">
+        <x:v>energy_gain_per_round</x:v>
+      </x:c>
+      <x:c r="K1" s="13" t="str">
+        <x:v>initial_ammo</x:v>
+      </x:c>
+      <x:c r="L1" s="13" t="str">
+        <x:v>max_ammo</x:v>
+      </x:c>
+      <x:c r="M1" s="13" t="str">
+        <x:v>ammo_gain_per_round</x:v>
+      </x:c>
+      <x:c r="N1" s="19" t="str">
+        <x:v>runtime_profile</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="s">
@@ -470,11 +597,39 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="N2" s="21" t="str">
+        <x:v>battle.HeroRuntimeProfile</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+      <x:c r="N3" s="23"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="s">
@@ -500,6 +655,27 @@
       <x:c r="G4" s="4" t="str">
         <x:v>View Prefab Key</x:v>
       </x:c>
+      <x:c r="H4" s="15" t="str">
+        <x:v>Initial Energy</x:v>
+      </x:c>
+      <x:c r="I4" s="15" t="str">
+        <x:v>Max Energy</x:v>
+      </x:c>
+      <x:c r="J4" s="15" t="str">
+        <x:v>Energy Gain Per Round</x:v>
+      </x:c>
+      <x:c r="K4" s="15" t="str">
+        <x:v>Initial Ammo</x:v>
+      </x:c>
+      <x:c r="L4" s="15" t="str">
+        <x:v>Max Ammo</x:v>
+      </x:c>
+      <x:c r="M4" s="15" t="str">
+        <x:v>Ammo Gain Per Round</x:v>
+      </x:c>
+      <x:c r="N4" s="25" t="str">
+        <x:v>Battle runtime profile</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="6">
@@ -521,6 +697,69 @@
       </x:c>
       <x:c r="G5" s="11" t="str">
         <x:v>pfb_char_player</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I5" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J5" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="27" t="str">
+        <x:v>Legacy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6"/>
+      <x:c r="B6" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>battle.hero.machine_gunner.name</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>pfb_char_player</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="27" t="str">
+        <x:v>MachineGunner</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/DataTables/Datas/battle.hero.xlsx
+++ b/DataTables/Datas/battle.hero.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae947acf4b104459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69b9650b887a4e08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -525,6 +525,10 @@
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="28" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="24" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -572,6 +576,18 @@
       <x:c r="N1" s="19" t="str">
         <x:v>runtime_profile</x:v>
       </x:c>
+      <x:c r="O1" t="str">
+        <x:v>reward_card_template_ids</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>reward_common_weight</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>reward_uncommon_weight</x:v>
+      </x:c>
+      <x:c r="R1" t="str">
+        <x:v>reward_rare_weight</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="s">
@@ -617,6 +633,18 @@
       </x:c>
       <x:c r="N2" s="21" t="str">
         <x:v>battle.HeroRuntimeProfile</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>(array#sep=,),int</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>int</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -630,6 +658,10 @@
       <x:c r="L3"/>
       <x:c r="M3"/>
       <x:c r="N3" s="23"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="s">
@@ -676,6 +708,18 @@
       <x:c r="N4" s="25" t="str">
         <x:v>Battle runtime profile</x:v>
       </x:c>
+      <x:c r="O4" t="str">
+        <x:v>Reward card template IDs</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>Common reward weight</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>Uncommon reward weight</x:v>
+      </x:c>
+      <x:c r="R4" t="str">
+        <x:v>Rare reward weight</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="6">
@@ -718,6 +762,18 @@
       </x:c>
       <x:c r="N5" s="27" t="str">
         <x:v>Legacy</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>3105,3108,3113,3115,3116,3118,3120,3123,3125,3157,3169,3171</x:v>
+      </x:c>
+      <x:c r="P5" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q5" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R5" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -761,6 +817,18 @@
       <x:c r="N6" s="27" t="str">
         <x:v>MachineGunner</x:v>
       </x:c>
+      <x:c r="O6" t="str">
+        <x:v>3206,3207,3208,3209,3210,3211,3212,3213,3214,3215,3216,3217,3218,3219,3220,3221,3222,3223,3224,3225,3226,3227,3228,3229,3230,3231,3232,3233,3234,3235,3236,3237,3238,3239,3240,3241,3242,3243,3244,3245,3246,3247,3248,3249,3250,3251,3252,3253,3254,3255,3256,3257,3258,3259,3260,3261,3262,3264,3265,3266,3267,3268,3269,3270,3271,3272,3273,3274,3275,3276,3277,3278,3279,3280,3281,3282</x:v>
+      </x:c>
+      <x:c r="P6" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q6" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R6" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
